--- a/Honda_Logi/Excel_Format/見積書(機種)_見積依頼.xlsx
+++ b/Honda_Logi/Excel_Format/見積書(機種)_見積依頼.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\01_hida_data\78_Honda_ロジ\01_PG\git\Honda_Logi\Excel_Format\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{9EEAD5F3-764F-40AE-8B2A-DBCC9E4C7C86}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AA1E9082-A0EA-4A51-98A9-95FBCA45828C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="1965" windowWidth="25440" windowHeight="15390" xr2:uid="{30C798AB-CC9F-4975-B461-26535877115E}"/>
   </bookViews>
@@ -192,10 +192,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
-    <numFmt numFmtId="180" formatCode="#,##0.0;[Red]\-#,##0.0"/>
-    <numFmt numFmtId="181" formatCode="#,##0.000;[Red]\-#,##0.000"/>
+    <numFmt numFmtId="176" formatCode="#,##0.0;[Red]\-#,##0.0"/>
+    <numFmt numFmtId="177" formatCode="#,##0.000;[Red]\-#,##0.000"/>
   </numFmts>
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -240,12 +240,6 @@
       <family val="3"/>
       <charset val="128"/>
     </font>
-    <font>
-      <sz val="10"/>
-      <name val="Meiryo UI"/>
-      <family val="3"/>
-      <charset val="128"/>
-    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -364,18 +358,15 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="3">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="38" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -418,53 +409,28 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="2" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="38" fontId="3" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
     <xf numFmtId="38" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="180" fontId="3" fillId="0" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="180" fontId="3" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="40" fontId="3" fillId="0" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="3" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="40" fontId="3" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="181" fontId="3" fillId="0" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="3" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="181" fontId="3" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
   </cellXfs>
-  <cellStyles count="3">
+  <cellStyles count="2">
     <cellStyle name="桁区切り" xfId="1" builtinId="6"/>
     <cellStyle name="標準" xfId="0" builtinId="0"/>
-    <cellStyle name="標準_HEPE設変追加部品'07,02月度" xfId="2" xr:uid="{040D7FA6-8F86-422E-9E50-89EC303D0579}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -835,22 +801,22 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B1:V19"/>
+  <dimension ref="B1:U4"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="9" style="1"/>
-    <col min="2" max="6" width="11.125" style="19" customWidth="1"/>
-    <col min="7" max="8" width="11.125" style="16" customWidth="1"/>
-    <col min="9" max="10" width="11.125" style="27" customWidth="1"/>
-    <col min="11" max="11" width="16.625" style="23" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="15.125" style="23" bestFit="1" customWidth="1"/>
-    <col min="13" max="17" width="11.125" style="21" customWidth="1"/>
-    <col min="18" max="20" width="11.125" style="25" customWidth="1"/>
-    <col min="21" max="21" width="9" style="25"/>
+    <col min="2" max="6" width="11.125" style="15" customWidth="1"/>
+    <col min="7" max="8" width="11.125" style="14" customWidth="1"/>
+    <col min="9" max="10" width="11.125" style="19" customWidth="1"/>
+    <col min="11" max="11" width="16.625" style="17" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="15.125" style="17" bestFit="1" customWidth="1"/>
+    <col min="13" max="17" width="11.125" style="16" customWidth="1"/>
+    <col min="18" max="20" width="11.125" style="18" customWidth="1"/>
+    <col min="21" max="21" width="9" style="18"/>
     <col min="22" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:22" x14ac:dyDescent="0.4">
+    <row r="1" spans="2:21" x14ac:dyDescent="0.4">
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
       <c r="D1" s="1"/>
@@ -872,7 +838,7 @@
       <c r="T1" s="1"/>
       <c r="U1" s="1"/>
     </row>
-    <row r="2" spans="2:22" x14ac:dyDescent="0.4">
+    <row r="2" spans="2:21" x14ac:dyDescent="0.4">
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
       <c r="D2" s="1"/>
@@ -894,7 +860,7 @@
       <c r="T2" s="1"/>
       <c r="U2" s="1"/>
     </row>
-    <row r="3" spans="2:22" x14ac:dyDescent="0.4">
+    <row r="3" spans="2:21" x14ac:dyDescent="0.4">
       <c r="B3" s="3"/>
       <c r="C3" s="3"/>
       <c r="D3" s="3"/>
@@ -918,7 +884,7 @@
       <c r="T3" s="7"/>
       <c r="U3" s="8"/>
     </row>
-    <row r="4" spans="2:22" x14ac:dyDescent="0.4">
+    <row r="4" spans="2:21" x14ac:dyDescent="0.4">
       <c r="B4" s="9" t="s">
         <v>1</v>
       </c>
@@ -977,337 +943,6 @@
         <v>19</v>
       </c>
       <c r="U4" s="13"/>
-    </row>
-    <row r="5" spans="2:22" x14ac:dyDescent="0.4">
-      <c r="B5" s="17"/>
-      <c r="C5" s="17"/>
-      <c r="D5" s="17"/>
-      <c r="E5" s="18"/>
-      <c r="F5" s="18"/>
-      <c r="G5" s="15"/>
-      <c r="H5" s="15"/>
-      <c r="I5" s="26"/>
-      <c r="J5" s="26"/>
-      <c r="K5" s="22"/>
-      <c r="L5" s="22"/>
-      <c r="M5" s="20"/>
-      <c r="N5" s="20"/>
-      <c r="O5" s="20"/>
-      <c r="P5" s="20"/>
-      <c r="Q5" s="20"/>
-      <c r="R5" s="24"/>
-      <c r="S5" s="24"/>
-      <c r="T5" s="24"/>
-      <c r="U5" s="24"/>
-    </row>
-    <row r="6" spans="2:22" x14ac:dyDescent="0.4">
-      <c r="B6" s="17"/>
-      <c r="C6" s="17"/>
-      <c r="D6" s="17"/>
-      <c r="E6" s="18"/>
-      <c r="F6" s="18"/>
-      <c r="G6" s="15"/>
-      <c r="H6" s="15"/>
-      <c r="I6" s="26"/>
-      <c r="J6" s="26"/>
-      <c r="K6" s="22"/>
-      <c r="L6" s="22"/>
-      <c r="M6" s="20"/>
-      <c r="N6" s="20"/>
-      <c r="O6" s="20"/>
-      <c r="P6" s="20"/>
-      <c r="Q6" s="20"/>
-      <c r="R6" s="24"/>
-      <c r="S6" s="24"/>
-      <c r="T6" s="24"/>
-      <c r="U6" s="24"/>
-    </row>
-    <row r="7" spans="2:22" x14ac:dyDescent="0.4">
-      <c r="B7" s="17"/>
-      <c r="C7" s="17"/>
-      <c r="D7" s="17"/>
-      <c r="E7" s="18"/>
-      <c r="F7" s="18"/>
-      <c r="G7" s="15"/>
-      <c r="H7" s="15"/>
-      <c r="I7" s="26"/>
-      <c r="J7" s="26"/>
-      <c r="K7" s="22"/>
-      <c r="L7" s="22"/>
-      <c r="M7" s="20"/>
-      <c r="N7" s="20"/>
-      <c r="O7" s="20"/>
-      <c r="P7" s="20"/>
-      <c r="Q7" s="20"/>
-      <c r="R7" s="24"/>
-      <c r="S7" s="24"/>
-      <c r="T7" s="24"/>
-      <c r="U7" s="24"/>
-    </row>
-    <row r="8" spans="2:22" x14ac:dyDescent="0.4">
-      <c r="B8" s="17"/>
-      <c r="C8" s="17"/>
-      <c r="D8" s="17"/>
-      <c r="E8" s="18"/>
-      <c r="F8" s="18"/>
-      <c r="G8" s="15"/>
-      <c r="H8" s="15"/>
-      <c r="I8" s="26"/>
-      <c r="J8" s="26"/>
-      <c r="K8" s="22"/>
-      <c r="L8" s="22"/>
-      <c r="M8" s="20"/>
-      <c r="N8" s="20"/>
-      <c r="O8" s="20"/>
-      <c r="P8" s="20"/>
-      <c r="Q8" s="20"/>
-      <c r="R8" s="24"/>
-      <c r="S8" s="24"/>
-      <c r="T8" s="24"/>
-      <c r="U8" s="24"/>
-    </row>
-    <row r="9" spans="2:22" x14ac:dyDescent="0.4">
-      <c r="B9" s="17"/>
-      <c r="C9" s="17"/>
-      <c r="D9" s="17"/>
-      <c r="E9" s="18"/>
-      <c r="F9" s="18"/>
-      <c r="G9" s="15"/>
-      <c r="H9" s="15"/>
-      <c r="I9" s="26"/>
-      <c r="J9" s="26"/>
-      <c r="K9" s="22"/>
-      <c r="L9" s="22"/>
-      <c r="M9" s="20"/>
-      <c r="N9" s="20"/>
-      <c r="O9" s="20"/>
-      <c r="P9" s="20"/>
-      <c r="Q9" s="20"/>
-      <c r="R9" s="24"/>
-      <c r="S9" s="24"/>
-      <c r="T9" s="24"/>
-      <c r="U9" s="24"/>
-    </row>
-    <row r="10" spans="2:22" x14ac:dyDescent="0.4">
-      <c r="B10" s="17"/>
-      <c r="C10" s="17"/>
-      <c r="D10" s="17"/>
-      <c r="E10" s="18"/>
-      <c r="F10" s="18"/>
-      <c r="G10" s="15"/>
-      <c r="H10" s="15"/>
-      <c r="I10" s="26"/>
-      <c r="J10" s="26"/>
-      <c r="K10" s="22"/>
-      <c r="L10" s="22"/>
-      <c r="M10" s="20"/>
-      <c r="N10" s="20"/>
-      <c r="O10" s="20"/>
-      <c r="P10" s="20"/>
-      <c r="Q10" s="20"/>
-      <c r="R10" s="24"/>
-      <c r="S10" s="24"/>
-      <c r="T10" s="24"/>
-      <c r="U10" s="24"/>
-    </row>
-    <row r="11" spans="2:22" x14ac:dyDescent="0.4">
-      <c r="B11" s="17"/>
-      <c r="C11" s="17"/>
-      <c r="D11" s="17"/>
-      <c r="E11" s="18"/>
-      <c r="F11" s="18"/>
-      <c r="G11" s="15"/>
-      <c r="H11" s="15"/>
-      <c r="I11" s="26"/>
-      <c r="J11" s="26"/>
-      <c r="K11" s="22"/>
-      <c r="L11" s="22"/>
-      <c r="M11" s="20"/>
-      <c r="N11" s="20"/>
-      <c r="O11" s="20"/>
-      <c r="P11" s="20"/>
-      <c r="Q11" s="20"/>
-      <c r="R11" s="24"/>
-      <c r="S11" s="24"/>
-      <c r="T11" s="24"/>
-      <c r="U11" s="24"/>
-    </row>
-    <row r="12" spans="2:22" x14ac:dyDescent="0.4">
-      <c r="B12" s="17"/>
-      <c r="C12" s="17"/>
-      <c r="D12" s="17"/>
-      <c r="E12" s="18"/>
-      <c r="F12" s="18"/>
-      <c r="G12" s="15"/>
-      <c r="H12" s="15"/>
-      <c r="I12" s="26"/>
-      <c r="J12" s="26"/>
-      <c r="K12" s="22"/>
-      <c r="L12" s="22"/>
-      <c r="M12" s="20"/>
-      <c r="N12" s="20"/>
-      <c r="O12" s="20"/>
-      <c r="P12" s="20"/>
-      <c r="Q12" s="20"/>
-      <c r="R12" s="24"/>
-      <c r="S12" s="24"/>
-      <c r="T12" s="24"/>
-      <c r="U12" s="24"/>
-    </row>
-    <row r="13" spans="2:22" x14ac:dyDescent="0.4">
-      <c r="B13" s="17"/>
-      <c r="C13" s="17"/>
-      <c r="D13" s="17"/>
-      <c r="E13" s="18"/>
-      <c r="F13" s="18"/>
-      <c r="G13" s="15"/>
-      <c r="H13" s="15"/>
-      <c r="I13" s="26"/>
-      <c r="J13" s="26"/>
-      <c r="K13" s="22"/>
-      <c r="L13" s="22"/>
-      <c r="M13" s="20"/>
-      <c r="N13" s="20"/>
-      <c r="O13" s="20"/>
-      <c r="P13" s="20"/>
-      <c r="Q13" s="20"/>
-      <c r="R13" s="24"/>
-      <c r="S13" s="24"/>
-      <c r="T13" s="24"/>
-      <c r="U13" s="24"/>
-      <c r="V13" s="14"/>
-    </row>
-    <row r="14" spans="2:22" x14ac:dyDescent="0.4">
-      <c r="B14" s="17"/>
-      <c r="C14" s="17"/>
-      <c r="D14" s="17"/>
-      <c r="E14" s="18"/>
-      <c r="F14" s="18"/>
-      <c r="G14" s="15"/>
-      <c r="H14" s="15"/>
-      <c r="I14" s="26"/>
-      <c r="J14" s="26"/>
-      <c r="K14" s="22"/>
-      <c r="L14" s="22"/>
-      <c r="M14" s="20"/>
-      <c r="N14" s="20"/>
-      <c r="O14" s="20"/>
-      <c r="P14" s="20"/>
-      <c r="Q14" s="20"/>
-      <c r="R14" s="24"/>
-      <c r="S14" s="24"/>
-      <c r="T14" s="24"/>
-      <c r="U14" s="24"/>
-    </row>
-    <row r="15" spans="2:22" x14ac:dyDescent="0.4">
-      <c r="B15" s="17"/>
-      <c r="C15" s="17"/>
-      <c r="D15" s="17"/>
-      <c r="E15" s="18"/>
-      <c r="F15" s="18"/>
-      <c r="G15" s="15"/>
-      <c r="H15" s="15"/>
-      <c r="I15" s="26"/>
-      <c r="J15" s="26"/>
-      <c r="K15" s="22"/>
-      <c r="L15" s="22"/>
-      <c r="M15" s="20"/>
-      <c r="N15" s="20"/>
-      <c r="O15" s="20"/>
-      <c r="P15" s="20"/>
-      <c r="Q15" s="20"/>
-      <c r="R15" s="24"/>
-      <c r="S15" s="24"/>
-      <c r="T15" s="24"/>
-      <c r="U15" s="24"/>
-    </row>
-    <row r="16" spans="2:22" x14ac:dyDescent="0.4">
-      <c r="B16" s="17"/>
-      <c r="C16" s="17"/>
-      <c r="D16" s="17"/>
-      <c r="E16" s="18"/>
-      <c r="F16" s="18"/>
-      <c r="G16" s="15"/>
-      <c r="H16" s="15"/>
-      <c r="I16" s="26"/>
-      <c r="J16" s="26"/>
-      <c r="K16" s="22"/>
-      <c r="L16" s="22"/>
-      <c r="M16" s="20"/>
-      <c r="N16" s="20"/>
-      <c r="O16" s="20"/>
-      <c r="P16" s="20"/>
-      <c r="Q16" s="20"/>
-      <c r="R16" s="24"/>
-      <c r="S16" s="24"/>
-      <c r="T16" s="24"/>
-      <c r="U16" s="24"/>
-    </row>
-    <row r="17" spans="2:21" x14ac:dyDescent="0.4">
-      <c r="B17" s="17"/>
-      <c r="C17" s="17"/>
-      <c r="D17" s="17"/>
-      <c r="E17" s="18"/>
-      <c r="F17" s="18"/>
-      <c r="G17" s="15"/>
-      <c r="H17" s="15"/>
-      <c r="I17" s="26"/>
-      <c r="J17" s="26"/>
-      <c r="K17" s="22"/>
-      <c r="L17" s="22"/>
-      <c r="M17" s="20"/>
-      <c r="N17" s="20"/>
-      <c r="O17" s="20"/>
-      <c r="P17" s="20"/>
-      <c r="Q17" s="20"/>
-      <c r="R17" s="24"/>
-      <c r="S17" s="24"/>
-      <c r="T17" s="24"/>
-      <c r="U17" s="24"/>
-    </row>
-    <row r="18" spans="2:21" x14ac:dyDescent="0.4">
-      <c r="B18" s="17"/>
-      <c r="C18" s="17"/>
-      <c r="D18" s="17"/>
-      <c r="E18" s="18"/>
-      <c r="F18" s="18"/>
-      <c r="G18" s="15"/>
-      <c r="H18" s="15"/>
-      <c r="I18" s="26"/>
-      <c r="J18" s="26"/>
-      <c r="K18" s="22"/>
-      <c r="L18" s="22"/>
-      <c r="M18" s="20"/>
-      <c r="N18" s="20"/>
-      <c r="O18" s="20"/>
-      <c r="P18" s="20"/>
-      <c r="Q18" s="20"/>
-      <c r="R18" s="24"/>
-      <c r="S18" s="24"/>
-      <c r="T18" s="24"/>
-      <c r="U18" s="24"/>
-    </row>
-    <row r="19" spans="2:21" x14ac:dyDescent="0.4">
-      <c r="B19" s="17"/>
-      <c r="C19" s="17"/>
-      <c r="D19" s="17"/>
-      <c r="E19" s="18"/>
-      <c r="F19" s="18"/>
-      <c r="G19" s="15"/>
-      <c r="H19" s="15"/>
-      <c r="I19" s="26"/>
-      <c r="J19" s="26"/>
-      <c r="K19" s="22"/>
-      <c r="L19" s="22"/>
-      <c r="M19" s="20"/>
-      <c r="N19" s="20"/>
-      <c r="O19" s="20"/>
-      <c r="P19" s="20"/>
-      <c r="Q19" s="20"/>
-      <c r="R19" s="24"/>
-      <c r="S19" s="24"/>
-      <c r="T19" s="24"/>
-      <c r="U19" s="24"/>
     </row>
   </sheetData>
   <phoneticPr fontId="4"/>
